--- a/docs/cadrage/equipe-28-sprint-backlog-v3.0.xlsx
+++ b/docs/cadrage/equipe-28-sprint-backlog-v3.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" firstSheet="6" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Garde" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="275">
   <si>
     <t>A</t>
   </si>
@@ -1497,6 +1497,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6468,7 +6469,9 @@
       <c r="C20" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="D20" s="20"/>
+      <c r="D20" s="20" t="s">
+        <v>140</v>
+      </c>
       <c r="E20" s="21">
         <v>2</v>
       </c>
@@ -6489,7 +6492,9 @@
       <c r="C21" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D21" s="20"/>
+      <c r="D21" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="E21" s="21">
         <v>1</v>
       </c>
@@ -6510,7 +6515,9 @@
       <c r="C22" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="D22" s="20"/>
+      <c r="D22" s="20" t="s">
+        <v>140</v>
+      </c>
       <c r="E22" s="21">
         <v>1</v>
       </c>
@@ -6531,7 +6538,9 @@
       <c r="C23" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="20"/>
+      <c r="D23" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="E23" s="21">
         <v>2</v>
       </c>
@@ -6552,7 +6561,9 @@
       <c r="C24" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="D24" s="20"/>
+      <c r="D24" s="20" t="s">
+        <v>138</v>
+      </c>
       <c r="E24" s="21">
         <v>1</v>
       </c>
@@ -6573,7 +6584,9 @@
       <c r="C25" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="D25" s="23"/>
+      <c r="D25" s="23" t="s">
+        <v>137</v>
+      </c>
       <c r="E25" s="24">
         <v>1</v>
       </c>
@@ -6594,7 +6607,9 @@
       <c r="C26" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="D26" s="23"/>
+      <c r="D26" s="23" t="s">
+        <v>137</v>
+      </c>
       <c r="E26" s="24">
         <v>2</v>
       </c>
@@ -6615,7 +6630,9 @@
       <c r="C27" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="D27" s="23"/>
+      <c r="D27" s="23" t="s">
+        <v>137</v>
+      </c>
       <c r="E27" s="24">
         <v>3</v>
       </c>
@@ -6636,7 +6653,9 @@
       <c r="C28" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="D28" s="23"/>
+      <c r="D28" s="23" t="s">
+        <v>139</v>
+      </c>
       <c r="E28" s="24">
         <v>3</v>
       </c>
@@ -6657,7 +6676,9 @@
       <c r="C29" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="D29" s="23"/>
+      <c r="D29" s="23" t="s">
+        <v>139</v>
+      </c>
       <c r="E29" s="24">
         <v>2</v>
       </c>
@@ -6678,7 +6699,9 @@
       <c r="C30" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="D30" s="26"/>
+      <c r="D30" s="26" t="s">
+        <v>139</v>
+      </c>
       <c r="E30" s="27">
         <v>2</v>
       </c>
@@ -6699,7 +6722,9 @@
       <c r="C31" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="D31" s="26"/>
+      <c r="D31" s="26" t="s">
+        <v>139</v>
+      </c>
       <c r="E31" s="27">
         <v>1</v>
       </c>
@@ -6926,7 +6951,9 @@
       <c r="C20" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="D20" s="20"/>
+      <c r="D20" s="20" t="s">
+        <v>141</v>
+      </c>
       <c r="E20" s="21">
         <v>2</v>
       </c>
@@ -6947,7 +6974,9 @@
       <c r="C21" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="D21" s="20"/>
+      <c r="D21" s="20" t="s">
+        <v>138</v>
+      </c>
       <c r="E21" s="21">
         <v>2</v>
       </c>
@@ -6968,7 +6997,9 @@
       <c r="C22" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="D22" s="20"/>
+      <c r="D22" s="20" t="s">
+        <v>138</v>
+      </c>
       <c r="E22" s="21">
         <v>1</v>
       </c>
@@ -6989,7 +7020,9 @@
       <c r="C23" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="D23" s="20"/>
+      <c r="D23" s="20" t="s">
+        <v>138</v>
+      </c>
       <c r="E23" s="21">
         <v>3</v>
       </c>
@@ -7010,7 +7043,9 @@
       <c r="C24" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="D24" s="20"/>
+      <c r="D24" s="20" t="s">
+        <v>138</v>
+      </c>
       <c r="E24" s="20">
         <v>2</v>
       </c>
@@ -7031,7 +7066,9 @@
       <c r="C25" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="D25" s="20"/>
+      <c r="D25" s="20" t="s">
+        <v>138</v>
+      </c>
       <c r="E25" s="20">
         <v>3</v>
       </c>
@@ -7052,7 +7089,9 @@
       <c r="C26" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="20"/>
+      <c r="D26" s="20" t="s">
+        <v>138</v>
+      </c>
       <c r="E26" s="20">
         <v>2</v>
       </c>
@@ -7073,7 +7112,9 @@
       <c r="C27" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="D27" s="20"/>
+      <c r="D27" s="20" t="s">
+        <v>141</v>
+      </c>
       <c r="E27" s="20">
         <v>3</v>
       </c>
@@ -7094,7 +7135,9 @@
       <c r="C28" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="D28" s="20"/>
+      <c r="D28" s="20" t="s">
+        <v>141</v>
+      </c>
       <c r="E28" s="20">
         <v>3</v>
       </c>
@@ -7384,7 +7427,9 @@
       <c r="C23" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="D23" s="20"/>
+      <c r="D23" s="20" t="s">
+        <v>140</v>
+      </c>
       <c r="E23" s="21">
         <v>2</v>
       </c>
@@ -7405,7 +7450,9 @@
       <c r="C24" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="D24" s="20"/>
+      <c r="D24" s="20" t="s">
+        <v>140</v>
+      </c>
       <c r="E24" s="20">
         <v>3</v>
       </c>
@@ -7426,7 +7473,9 @@
       <c r="C25" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="D25" s="20"/>
+      <c r="D25" s="20" t="s">
+        <v>140</v>
+      </c>
       <c r="E25" s="20">
         <v>3</v>
       </c>
@@ -7447,7 +7496,9 @@
       <c r="C26" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="D26" s="20"/>
+      <c r="D26" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="E26" s="20">
         <v>2</v>
       </c>
@@ -7468,7 +7519,9 @@
       <c r="C27" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="D27" s="20"/>
+      <c r="D27" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="E27" s="20">
         <v>3</v>
       </c>
@@ -7489,7 +7542,9 @@
       <c r="C28" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="D28" s="20"/>
+      <c r="D28" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="E28" s="20">
         <v>4</v>
       </c>
@@ -7510,7 +7565,9 @@
       <c r="C29" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="D29" s="20"/>
+      <c r="D29" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="E29" s="20">
         <v>2</v>
       </c>
